--- a/data/excel/Autommerce_Partners_Saudi_Arabia.xlsx
+++ b/data/excel/Autommerce_Partners_Saudi_Arabia.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partners" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partners'!$A$1:$D$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partners'!$A$1:$D$119</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D116"/>
+  <dimension ref="A1:D119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2026,39 +2026,39 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>i95Dev</t>
+          <t>Mind Digital Group</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>https://i95dev.com</t>
+          <t>https://minddigital.com</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>consenso Consulting</t>
+          <t>VML</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>https://consenso.de</t>
+          <t>https://vml.com</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -2070,17 +2070,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Q5 Partners</t>
+          <t>SEIDOR</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>https://q5arabia.sa</t>
+          <t>https://seidor.com</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Consulting &amp; Strategy Firms</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -2092,61 +2092,61 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>UIUX Studio</t>
+          <t>i95Dev</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>https://uiux.studio</t>
+          <t>https://i95dev.com</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce CRO &amp; UX/UI Agencies</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>TekRevol</t>
+          <t>consenso Consulting</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>https://tekrevol.com</t>
+          <t>https://consenso.de</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>ScienceSoft</t>
+          <t>Q5 Partners</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>https://scnsoft.com</t>
+          <t>https://q5arabia.sa</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Consulting &amp; Strategy Firms</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -2158,12 +2158,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>DOOR3</t>
+          <t>UIUX Studio</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>https://door3.com</t>
+          <t>https://uiux.studio</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -2173,46 +2173,46 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Apollo Solutions</t>
+          <t>TekRevol</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>https://apollo-solutions.net</t>
+          <t>https://tekrevol.com</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Automation &amp; Workflow Consulting Firms</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>IACo</t>
+          <t>ScienceSoft</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>https://iaco.com</t>
+          <t>https://scnsoft.com</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Mavenbird</t>
+          <t>DOOR3</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>https://mavenbird.com</t>
+          <t>https://door3.com</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -2246,17 +2246,17 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>intouch</t>
+          <t>Apollo Solutions</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>https://intouchmena.com</t>
+          <t>https://apollo-solutions.net</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce Automation &amp; Workflow Consulting Firms</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>LtsThink</t>
+          <t>IACo</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>https://ltsthink.com</t>
+          <t>https://iaco.com</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -2290,34 +2290,34 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Mavenbird</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>https://steps-ksa.com</t>
+          <t>https://mavenbird.com</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce CRO &amp; UX/UI Agencies</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Optimizera</t>
+          <t>intouch</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>https://optimizera.sa</t>
+          <t>https://intouchmena.com</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -2327,19 +2327,19 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Adlogic</t>
+          <t>LtsThink</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>https://adlogicco.com</t>
+          <t>https://ltsthink.com</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>ARQQA</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>https://arqqa.net</t>
+          <t>https://steps-ksa.com</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -2371,46 +2371,46 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Jmhour Lab</t>
+          <t>Optimizera</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>https://jmhour.com</t>
+          <t>https://optimizera.sa</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce CRO &amp; UX/UI Agencies</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Tasawk</t>
+          <t>Adlogic</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>https://tasawk.com.sa</t>
+          <t>https://adlogicco.com</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -2422,39 +2422,39 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>24Seven Commerce</t>
+          <t>ARQQA</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>https://24sevencommerce.com</t>
+          <t>https://arqqa.net</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Automation &amp; Workflow Consulting Firms</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Liquid Havas Market</t>
+          <t>Jmhour Lab</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>https://liquidhavas.com</t>
+          <t>https://jmhour.com</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
+          <t>Ecommerce CRO &amp; UX/UI Agencies</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -2466,17 +2466,17 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>24TTL / 24.online</t>
+          <t>Tasawk</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>https://24ttl.net</t>
+          <t>https://tasawk.com.sa</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -2488,17 +2488,17 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Deviant Digital</t>
+          <t>24Seven Commerce</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>https://deviantdigital.io</t>
+          <t>https://24sevencommerce.com</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Digital Marketing Agencies</t>
+          <t>Ecommerce Automation &amp; Workflow Consulting Firms</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -2510,105 +2510,105 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>DigiMotive</t>
+          <t>Liquid Havas Market</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>https://digimotive.ae</t>
+          <t>https://liquidhavas.com</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Personalization &amp; Customer Experience Agencies</t>
+          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Digital Domingo</t>
+          <t>24TTL / 24.online</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>https://digitaldomingo.com</t>
+          <t>https://24ttl.net</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce CRO &amp; Conversion Optimization Agencies</t>
+          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Alvanon</t>
+          <t>Deviant Digital</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>https://alvanon.com</t>
+          <t>https://deviantdigital.io</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Sizing, Fit &amp; Returns Optimization Specialists</t>
+          <t>Fashion Ecommerce Digital Marketing Agencies</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Persona AI</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Happy Go Lucky</t>
+          <t>DigiMotive</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>https://happygoluckyltd.com</t>
+          <t>https://digimotive.ae</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Merchandising &amp; Styling Consultants</t>
+          <t>Fashion Ecommerce Personalization &amp; Customer Experience Agencies</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Persona AI</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Perspektive Agency</t>
+          <t>Digital Domingo</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>https://perspektiveagency.com</t>
+          <t>https://digitaldomingo.com</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
+          <t>Fashion Ecommerce CRO &amp; Conversion Optimization Agencies</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -2620,61 +2620,61 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Nomo Media</t>
+          <t>Alvanon</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>https://nomomediasa.com</t>
+          <t>https://alvanon.com</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
+          <t>Fashion Ecommerce Sizing, Fit &amp; Returns Optimization Specialists</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Persona AI</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>crēation LLC</t>
+          <t>Happy Go Lucky</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>https://creation.sa</t>
+          <t>https://happygoluckyltd.com</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce CRO &amp; Conversion Optimization Agencies</t>
+          <t>Fashion Ecommerce Merchandising &amp; Styling Consultants</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Persona AI</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>We Make Websites</t>
+          <t>Perspektive Agency</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>https://wemakewebsites.com</t>
+          <t>https://perspektiveagency.com</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -2686,39 +2686,39 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Internet Solutions</t>
+          <t>Nomo Media</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>https://is.net.sa</t>
+          <t>https://nomomediasa.com</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Cartello</t>
+          <t>crēation LLC</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>https://cartello.io</t>
+          <t>https://creation.sa</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce SEO Agencies &amp; Consultants</t>
+          <t>Fashion Ecommerce CRO &amp; Conversion Optimization Agencies</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -2730,17 +2730,17 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>e-Arabization</t>
+          <t>We Make Websites</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>https://e-arabization.com</t>
+          <t>https://wemakewebsites.com</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -2752,17 +2752,17 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>EDM</t>
+          <t>Internet Solutions</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>https://edm-tech.com</t>
+          <t>https://is.net.sa</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -2774,39 +2774,39 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Centric</t>
+          <t>Cartello</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>https://centricdxb.com</t>
+          <t>https://cartello.io</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Ecommerce SEO Agencies &amp; Consultants</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Intwo</t>
+          <t>e-Arabization</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>https://intwo.cloud</t>
+          <t>https://e-arabization.com</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -2818,61 +2818,61 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>scandiweb</t>
+          <t>EDM</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>https://scandiweb.com</t>
+          <t>https://edm-tech.com</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Gravityer</t>
+          <t>Centric</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>https://gravityer.com</t>
+          <t>https://centricdxb.com</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Valtech</t>
+          <t>Intwo</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>https://valtech.com</t>
+          <t>https://intwo.cloud</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -2884,17 +2884,17 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Incubeta</t>
+          <t>scandiweb</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>https://incubeta.com</t>
+          <t>https://scandiweb.com</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -2906,17 +2906,17 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>ArabyAds</t>
+          <t>Gravityer</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>https://arabyads.com</t>
+          <t>https://gravityer.com</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -2928,17 +2928,17 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>LUMINA Commerce</t>
+          <t>Valtech</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>https://luminacommerce.com</t>
+          <t>https://valtech.com</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -2950,17 +2950,17 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Dtech Systems</t>
+          <t>Incubeta</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>https://dtechsystems.co</t>
+          <t>https://incubeta.com</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -2972,27 +2972,93 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>ArabyAds</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>https://arabyads.com</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>LUMINA Commerce</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>https://luminacommerce.com</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce Website Development Agencies</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Dtech Systems</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>https://dtechsystems.co</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce Website Development Agencies</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
           <t>eCre8</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>https://ecre8.io</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
         <is>
           <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D116"/>
+  <autoFilter ref="A1:D119"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/excel/Autommerce_Partners_Saudi_Arabia.xlsx
+++ b/data/excel/Autommerce_Partners_Saudi_Arabia.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partners" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partners'!$A$1:$D$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partners'!$A$1:$D$124</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D119"/>
+  <dimension ref="A1:D124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3057,8 +3057,118 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Daam Al-Arabia</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>https://daam.com.sa</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce CRO &amp; UX/UI Agencies</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Autommerce OS</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>The i.o agency</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>https://theioagency.com</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce Website Development Agencies</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Web Katalyst</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>https://webkatalyst.com</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce System Integration Companies</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Ignite</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>https://ignite.sa</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce System Integration Companies</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Clicko Digital</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>https://clickodigital.com</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce System Integration Companies</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D119"/>
+  <autoFilter ref="A1:D124"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/excel/Autommerce_Partners_Saudi_Arabia.xlsx
+++ b/data/excel/Autommerce_Partners_Saudi_Arabia.xlsx
@@ -7,10 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partners" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company details" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision makers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partners'!$A$1:$D$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Company details'!$A$1:$G$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decision makers'!$A$1:$G$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,8 +30,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,10 +68,10 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -427,19 +435,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D124"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="72" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Company Name</t>
@@ -458,6 +470,21 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Product Fit</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Emails</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
         </is>
       </c>
     </row>
@@ -482,6 +509,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -504,6 +534,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -526,6 +559,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -548,6 +584,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -570,6 +609,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -592,6 +634,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -614,6 +659,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -636,6 +684,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -658,6 +709,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -680,6 +734,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -702,6 +759,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -724,6 +784,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -746,6 +809,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -768,6 +834,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -790,6 +859,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -812,6 +884,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -834,6 +909,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -856,6 +934,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -878,6 +959,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -900,6 +984,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -922,6 +1009,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -944,6 +1034,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -966,6 +1059,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -988,6 +1084,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1010,6 +1109,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1032,6 +1134,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1054,6 +1159,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1076,6 +1184,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1098,6 +1209,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1120,6 +1234,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1142,6 +1259,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1164,6 +1284,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1186,6 +1309,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1208,6 +1334,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1230,6 +1359,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1252,6 +1384,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1274,6 +1409,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1296,6 +1434,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1318,6 +1459,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1340,6 +1484,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1362,6 +1509,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1384,6 +1534,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1406,6 +1559,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1428,6 +1584,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1450,6 +1609,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1472,6 +1634,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1494,6 +1659,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1516,6 +1684,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1538,6 +1709,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1560,6 +1734,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1582,6 +1759,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1604,6 +1784,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1626,6 +1809,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1648,6 +1834,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -1670,6 +1859,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -1692,6 +1884,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1714,6 +1909,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -1736,6 +1934,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -1758,6 +1959,9 @@
           <t>Persona AI</t>
         </is>
       </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -1780,6 +1984,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -1802,6 +2009,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -1824,6 +2034,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -1846,6 +2059,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>general@nasam.co</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>+966 55 009 0039</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nasam-co</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -1868,6 +2096,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>hello@tarjama.com; sales@tarjama.com</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>+966 11 520 2874; +971 4 561 6821; +962 79 953 2572; +974 6651 4128; +961 4 715 999; +1 514 917 5271; +33 6 16 59 82 60</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tarjama</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -1890,6 +2133,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>info@revton.com</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>+962 620 077 11; +971 52 6967 470; +1 571 301 9082</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/revtonco</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -1912,6 +2170,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>hello@digitalorks.com</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>+971 4 431 8653</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/digitalorks</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -1934,6 +2207,17 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>hello@rndecommerce.com</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rnd-ecommerce-fulfillment</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -1956,6 +2240,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>hello@acquisit.io</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>+971 45 664 822</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/acquisit-advertising</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -1978,6 +2277,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>hello@nawawistudio.com</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>+966 54 300 7774</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nawawi-studio</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2000,6 +2314,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>sales@webkul.com</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>+1 914 353 1684; +91 9870284067</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/webkul</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2022,6 +2351,17 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>contact@ps-agency.ai</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ps-agency-ai</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2044,6 +2384,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>hinewyork@minddigital.com; hilondon@mindigital.com; hidubai@minddigital.com; hidelhi@mindigital.com</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>+1 212 796 6904; +1 800 245 2032; +44 207 849 6867; +44 7402 919 299; +971 5882 91395; +91 11 4100 3450; +91 956 087 5588</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mind-digital-group</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2066,6 +2421,13 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vml</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2088,6 +2450,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>info@seidor.com</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>+34 93 304 32 22</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/seidor</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2110,6 +2487,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>info@i95dev.com</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>+1 301 760 7499</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/i95dev</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2132,6 +2524,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>mail@consenso.de</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>+49 521 2606 0</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/consensoconsulting</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2154,6 +2561,17 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>arabia@q5partners.com</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/q5-arabia</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -2176,6 +2594,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>sales@uiux.studio</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>+971 56 647 7802</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ui-ux-studio</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -2198,6 +2631,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>info@tekrevol.com</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>+1 737 386 9583; +1 346 241 7474; +1 737 390 0072</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tekrevol</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -2220,6 +2668,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>contact@scnsoft.com; ksa@scnsoft.com; eu@scnsoft.com; nordics@scnsoft.com</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>+1 214 306 6837; +1 972 454 4730; +966 800 880 3035</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sciencesoft</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -2242,6 +2705,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>projects@door3.com</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>+1 212 673 1818</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/door3</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -2264,6 +2742,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>info@apollo-solutions.net</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>+966 53 777 4368; +90 552 833 0233; +963 933 733 818</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/apollo-solutions-sa</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -2286,6 +2779,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>info@iaco.com</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>+966 12 211 9555</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/international-applications-company-iaco</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -2308,6 +2816,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>sales@mavenbird.com</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>+91 9512033377</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mavenbird-technologies</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -2330,6 +2853,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>info@intouchmena.com</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>+974 4434 1021; +961 4 444 097; +966 56 642 5310</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/intouch-mena</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -2352,6 +2890,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>info@ltsthink.com</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>+966 55 252 5261</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ltsthink</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -2374,6 +2927,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>info@steps-ksa.com</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>+966 56 835 5046</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/steps-saudi</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -2396,6 +2964,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>ammar@optimizera.com</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>+966 54 958 5421</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/optimizera</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -2418,6 +3001,17 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>mahmoud@adlogicco.com</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>+20 103 303 3995</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -2440,6 +3034,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>info@arqqa.net</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>+20 2 2418 9939</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/digital-marketing-social-media-managment-egypt</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -2462,6 +3071,17 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>+966 59 815 6207</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jmhour-lab-%D8%AC%D9%85%D9%87%D9%88%D8%B1-%D9%84%D8%A7%D8%A8</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -2484,6 +3104,17 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>+966 54 066 4139</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tasawk</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -2506,6 +3137,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -2528,6 +3162,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -2550,6 +3187,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E96" s="2" t="inlineStr"/>
+      <c r="F96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -2572,6 +3212,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -2594,6 +3237,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -2616,6 +3262,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -2638,6 +3287,9 @@
           <t>Persona AI</t>
         </is>
       </c>
+      <c r="E100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -2660,6 +3312,9 @@
           <t>Persona AI</t>
         </is>
       </c>
+      <c r="E101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -2682,6 +3337,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -2704,6 +3362,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -2726,6 +3387,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E104" s="2" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -2748,6 +3412,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E105" s="2" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -2770,6 +3437,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -2792,6 +3462,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -2814,6 +3487,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -2836,6 +3512,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E109" s="2" t="inlineStr"/>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -2858,6 +3537,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -2880,6 +3562,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E111" s="2" t="inlineStr"/>
+      <c r="F111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -2902,6 +3587,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -2924,6 +3612,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E113" s="2" t="inlineStr"/>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -2946,6 +3637,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E114" s="2" t="inlineStr"/>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -2968,6 +3662,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E115" s="2" t="inlineStr"/>
+      <c r="F115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -2990,6 +3687,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -3012,6 +3712,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E117" s="2" t="inlineStr"/>
+      <c r="F117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -3034,6 +3737,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -3056,6 +3762,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E119" s="2" t="inlineStr"/>
+      <c r="F119" s="2" t="inlineStr"/>
+      <c r="G119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -3078,6 +3787,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -3100,6 +3812,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E121" s="2" t="inlineStr"/>
+      <c r="F121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -3122,6 +3837,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -3144,6 +3862,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E123" s="2" t="inlineStr"/>
+      <c r="F123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -3166,9 +3887,2026 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E124" s="2" t="inlineStr"/>
+      <c r="F124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D124"/>
+  <autoFilter ref="A1:G124"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F4E79"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G71"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Khaled Alashgr</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kashgr</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Head of Seller Services</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Nasam</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://nasam.co</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Fahad AL-Qaramseh</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fahad-al-qaramseh-05300441</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Director of Partnerships and Alliances</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Tarjama</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://tarjama.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Michel Khoury</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mfk20</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>VP of Marketing</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Tarjama</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://tarjama.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Nour Al Hassan</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nour-al-hassan-106778138</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Tarjama</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://tarjama.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Bilal Kasih</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bilalkasih</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Revton</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://revton.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Shadi Hamouri</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shadi-hamouri-52020770</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Director of Business Development</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Revton</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://revton.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Shaker Alkhatib</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shakeralkhatib</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Director</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Revton</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://revton.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Ayman Albarbary</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>ayman@digitalorks.com</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aymanalbarbary</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Digital Orks</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://digitalorks.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Mohammed Jarkas</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mjarkas</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Digital Orks</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://digitalorks.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Betül Gümüş</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/betül-gümüş-3b444045</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>RND E-Commerce</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://rndecommerce.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Zeynep Sare Erdoğan</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/zeynepsareerdogan</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Director of Growth and Partnerships</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>RND E-Commerce</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://rndecommerce.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Edouard Daou</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/edouard-daou</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder, Managing Partner KSA</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Acquisit</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://acquisit.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Marie Franchaud</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>BD and Marketing Manager</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Acquisit</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://acquisit.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Monika Formanowicz</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Digital Marketing Director</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Acquisit</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://acquisit.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Timothée Desormeaux</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/timothée-desormeaux-4390862</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder and Managing Partner</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Acquisit</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://acquisit.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Rayan Nawawi</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rayan-nawawi</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Creative Director</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Nawawi Studio</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://nawawistudio.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Wail Nawawi</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/wail-nawawi-61774aba</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder and Account Director</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Nawawi Studio</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://nawawistudio.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Abhishek Singh</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Vice President, E-Commerce</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Webkul</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>https://webkul.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Ajay Kumar</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>VP, E-commerce</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Webkul</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>https://webkul.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Prakash Sahu</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/prakash-sahu-956703a</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Webkul</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>https://webkul.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Rahul Gupta</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Head of Business Development</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Webkul</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>https://webkul.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Saurav Pathak</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Vice President, Product and Sales</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Webkul</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>https://webkul.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Sushil Kumar</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Vice President, Sales and Product</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Webkul</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>https://webkul.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Vinay Yadav</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vinayrks</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Webkul</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>https://webkul.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Vipin Sahu</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vipinsahu</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Webkul</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>https://webkul.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Pedro Duarte</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr"/>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pedroduarteee</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Founding Creative Director</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>PS Agency</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>https://ps-agency.ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Yusuf Javed</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>yusuf@minddigital.com</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/yusufjaved</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Director</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Mind Digital Group</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>https://minddigital.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Eric Campbell</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>CEO, VML North America</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>VML</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>https://vml.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Jon Cook</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jonvml</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Global CEO</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>VML</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>https://vml.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Naomi Troni</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>naomi.troni@vml.com</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/naomitroni</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Global Chief Marketing Officer</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>VML</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>https://vml.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Javier Navarro</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>General Manager of International Operations</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>SEIDOR</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>https://seidor.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Josep Benito</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Executive Chairman</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>SEIDOR</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>https://seidor.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Sergi Biosca</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sergibiosca</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>SEIDOR</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>https://seidor.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Syed Shaukath</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/syed-shaukath-84682ab</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Vice President of Sales</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>i95Dev</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>https://i95dev.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Vanit Kumar</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vanit-kumar</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>i95Dev</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>https://i95dev.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Vishnu Modi</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vishnu-modi</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>VP of Marketing</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>i95Dev</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>https://i95dev.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Achim Sieren</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>consenso Consulting</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>https://consenso.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Andreas Lorch</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr"/>
+      <c r="D39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>consenso Consulting</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>https://consenso.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Marc Weber</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>consenso Consulting</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>https://consenso.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Muhammet Kir</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr"/>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>consenso Consulting</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>https://consenso.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Rainer Nolte</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director and Co-founder</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>consenso Consulting</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>https://consenso.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Abdullah Alghamdi</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr"/>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Head of Strategic Advisory and Growth</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Q5 Partners</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>https://q5arabia.sa</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Chris Parsons</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chrisparsonsq5orgdesignexpert</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Partner</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Q5 Partners</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>https://q5arabia.sa</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Scott Kennedy</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr"/>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/scottkennedy918</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director, Q5 Arabia</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Q5 Partners</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>https://q5arabia.sa</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Sharon Rice-Oxley</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Managing Partner</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Q5 Partners</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>https://q5arabia.sa</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Harminder Singh</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr"/>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/uiuxstudio</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Director</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>UIUX Studio</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>https://uiux.studio</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Abeer Raza</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder and CMO</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>TekRevol</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>https://tekrevol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Asim Rais Siddiqui</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr"/>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/asimrsiddiqui</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder and CTO</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>TekRevol</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>https://tekrevol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Chris Brogan</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chris-brogan-16a495166</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>TekRevol</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>https://tekrevol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Ryan Shirzadi</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr"/>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ryangshirzadi</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Regional Partner</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>TekRevol</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>https://tekrevol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Max Eliseev</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maxeliseev</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer, ScienceSoft EMEA</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>ScienceSoft</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>https://scnsoft.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Nick Kurayev</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr"/>
+      <c r="D53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>ScienceSoft</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>https://scnsoft.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Wade Brantley</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer, ScienceSoft USA</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>ScienceSoft</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>https://scnsoft.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Alex Asianov</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr"/>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alexasianov</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Founder and President</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>DOOR3</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>https://door3.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Abdullah Ar Bindawood</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>IACo</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>https://iaco.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Majed M. AlTahan</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr"/>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/majedmaltahan</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>IACo</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>https://iaco.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Harshil Patwa</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/harshilpatwa</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Mavenbird</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>https://mavenbird.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Louay Chehab</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr"/>
+      <c r="D59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Strategic Partner</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>intouch</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>https://intouchmena.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Vany Sawma</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vany-sawma-34b99a14</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Head of Growth</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>intouch</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>https://intouchmena.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Victor D. Sawma</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr"/>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/victorsawma</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder and CTO</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>intouch</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>https://intouchmena.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Zayd Ghobar</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/zayd-ghobar-9a889974</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>intouch</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>https://intouchmena.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Baraa Kheshaifaty</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr"/>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/baraakheshifaty</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Creative Director and Cofounder</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>LtsThink</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>https://ltsthink.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Mostafa Sofy</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mostafasofy</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>https://steps-ksa.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Ammar Awaeer</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>ammar@optimizera.com</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ammar-awaeer-67639a199</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Head of Digital Marketing Analytics</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Optimizera</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>https://optimizera.sa</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Majd Fallaha</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Director of eCommerce Marketing and Analytics</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Optimizera</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>https://optimizera.sa</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Mahmoud Gamal Al-Asklany</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>mahmoud@adlogicco.com</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mo91gamal</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Head of Strategy</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Adlogic</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>https://adlogicco.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Nadeem Abdin</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr"/>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>ARQQA</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>https://arqqa.net</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Wael Saad</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr"/>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/wasaad</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>ARQQA</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>https://arqqa.net</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Feras Al-Harbi</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr"/>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ferasfa</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Jmhour Lab</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>https://jmhour.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Tamim Alghanam</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr"/>
+      <c r="D71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder and Board Member</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Jmhour Lab</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>https://jmhour.com</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G71"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>